--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\4- MANUTENÇÃO 2026\Indicadores 2025-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2174ED39EE86703450359D9A0F793897CC550717" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" tabRatio="763" activeTab="5"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados_OS" sheetId="1" r:id="rId1"/>
@@ -19,10 +20,23 @@
     <sheet name="Tratamento de Dados 2026" sheetId="6" r:id="rId5"/>
     <sheet name="Graficos de Custos 2026" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -314,7 +328,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -508,11 +522,10 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -522,9 +535,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -541,11 +551,8 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -560,7 +567,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -570,7 +576,6 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1089,7 +1094,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Controle de Custos de Manutencão.xlsx]Planilha2!Tabela dinâmica15</c:name>
+    <c:name>[manutencao.xlsx]Planilha2!Tabela dinâmica15</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -4016,6 +4021,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="38"/>
@@ -4068,6 +4114,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="39"/>
@@ -4120,6 +4207,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="40"/>
@@ -4172,6 +4300,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="41"/>
@@ -4245,6 +4414,46 @@
             </a:sp3d>
           </c:spPr>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -4335,7 +4544,60 @@
             </c:extLst>
           </c:dPt>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -4516,7 +4778,60 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -4697,7 +5012,60 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -4878,7 +5246,60 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -8731,7 +9152,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8882,7 +9302,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -9532,9 +9951,7 @@
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -9773,7 +10190,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9904,9 +10320,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-6BA2-4EBA-BA61-225F9CCECC47}"/>
                 </c:ext>
@@ -9928,9 +10342,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-93B7-4219-9DE6-B18022BB97A7}"/>
                 </c:ext>
@@ -10041,7 +10453,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
@@ -10218,9 +10629,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-6BA2-4EBA-BA61-225F9CCECC47}"/>
                 </c:ext>
@@ -10241,9 +10650,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-6BA2-4EBA-BA61-225F9CCECC47}"/>
                 </c:ext>
@@ -10264,9 +10671,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-6BA2-4EBA-BA61-225F9CCECC47}"/>
                 </c:ext>
@@ -11039,9 +11444,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-9DCB-478D-BCC8-88356239B50E}"/>
                 </c:ext>
@@ -11316,9 +11719,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000013-6BA2-4EBA-BA61-225F9CCECC47}"/>
                 </c:ext>
@@ -11339,9 +11740,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000014-6BA2-4EBA-BA61-225F9CCECC47}"/>
                 </c:ext>
@@ -11362,9 +11761,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000015-6BA2-4EBA-BA61-225F9CCECC47}"/>
                 </c:ext>
@@ -15727,7 +16124,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -15764,7 +16167,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -15796,7 +16205,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2"/>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -15828,7 +16243,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Gráfico 5"/>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -15865,7 +16286,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -15897,7 +16324,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2"/>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -15929,7 +16362,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3"/>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -15950,7 +16389,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Manutencao" refreshedDate="46078.332756481483" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="14">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Manutencao" refreshedDate="46078.332756481483" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="14" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B11:I23" sheet="Tratamento de Dados 2025"/>
   </cacheSource>
@@ -16150,7 +16589,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Tabela dinâmica15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:F20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0">
@@ -16416,35 +16855,38 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:L48" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
-  <autoFilter ref="A1:L48"/>
-  <sortState ref="A2:L43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:L48" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+  <autoFilter ref="A1:L48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L43">
     <sortCondition ref="A1:A43"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" name="OS" dataDxfId="36"/>
-    <tableColumn id="2" name="Data de Abertura" dataDxfId="35"/>
-    <tableColumn id="12" name="Data de Fechamento" dataDxfId="34"/>
-    <tableColumn id="10" name="Ano" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="OS" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Data de Abertura" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Data de Fechamento" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Ano" dataDxfId="33">
       <calculatedColumnFormula>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" name="Mês Fechamento" dataDxfId="32">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Mês Fechamento" dataDxfId="32">
       <calculatedColumnFormula>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Equipamento" dataDxfId="31"/>
-    <tableColumn id="4" name="Tag - Identificação" dataDxfId="30"/>
-    <tableColumn id="5" name="Tipo_Manutencao" dataDxfId="29"/>
-    <tableColumn id="6" name="Custo_MO" dataDxfId="28" dataCellStyle="Moeda"/>
-    <tableColumn id="7" name="Custo_Materiais" dataDxfId="27" dataCellStyle="Moeda"/>
-    <tableColumn id="8" name="Tempo_Parada_h" dataDxfId="26">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Equipamento" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tag - Identificação" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tipo_Manutencao" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Custo_MO" dataDxfId="28" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Custo_Materiais" dataDxfId="27" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Tempo_Parada_h" dataDxfId="26">
       <calculatedColumnFormula>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" name="Custo_Total" dataDxfId="25" dataCellStyle="Moeda">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Custo_Total" dataDxfId="25" dataCellStyle="Moeda">
       <calculatedColumnFormula>I2+J2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16453,31 +16895,31 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabela4" displayName="Tabela4" ref="A11:J23" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" dataCellStyle="Moeda">
-  <autoFilter ref="A11:J23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela4" displayName="Tabela4" ref="A11:J23" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" dataCellStyle="Moeda">
+  <autoFilter ref="A11:J23" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="10">
-    <tableColumn id="10" name="Faturemento Mensal" dataDxfId="22" dataCellStyle="Moeda"/>
-    <tableColumn id="1" name="Ano"/>
-    <tableColumn id="2" name="Mês"/>
-    <tableColumn id="3" name="Corretiva não programada" dataDxfId="21" dataCellStyle="Moeda">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Faturemento Mensal" dataDxfId="22" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Ano"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Mês"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Corretiva não programada" dataDxfId="21" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="Corretiva programada" dataDxfId="20" dataCellStyle="Moeda">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Corretiva programada" dataDxfId="20" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="Preventiva" dataDxfId="19" dataCellStyle="Moeda">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Preventiva" dataDxfId="19" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="Preditiva" dataDxfId="18" dataCellStyle="Moeda">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Preditiva" dataDxfId="18" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="Melhoria de Máquinas" dataDxfId="17" dataCellStyle="Moeda">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Melhoria de Máquinas" dataDxfId="17" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="0,5% do Faturamento Bruto Mensal" dataDxfId="16" dataCellStyle="Moeda">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="0,5% do Faturamento Bruto Mensal" dataDxfId="16" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" name="total" dataDxfId="15" dataCellStyle="Moeda">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="total" dataDxfId="15" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUM(Tabela4[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16486,14 +16928,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabela5" displayName="Tabela5" ref="B2:D7" totalsRowShown="0">
-  <autoFilter ref="B2:D7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela5" displayName="Tabela5" ref="B2:D7" totalsRowShown="0">
+  <autoFilter ref="B2:D7" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Tipo de manutenção"/>
-    <tableColumn id="2" name="Custo Total por tipo de manutenção (R$)" dataDxfId="14" dataCellStyle="Moeda">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Tipo de manutenção"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Custo Total por tipo de manutenção (R$)" dataDxfId="14" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela5[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2025'!$D$1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Percentual de custo total por tipo" dataDxfId="13" dataCellStyle="Porcentagem">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Percentual de custo total por tipo" dataDxfId="13" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela5[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela5[Custo Total por tipo de manutenção (R$)])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16502,31 +16944,31 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela43" displayName="Tabela43" ref="A11:J23" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" dataCellStyle="Moeda">
-  <autoFilter ref="A11:J23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabela43" displayName="Tabela43" ref="A11:J23" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" dataCellStyle="Moeda">
+  <autoFilter ref="A11:J23" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="10">
-    <tableColumn id="11" name="Faturamento Mensal" dataDxfId="10" dataCellStyle="Moeda"/>
-    <tableColumn id="1" name="Ano" dataDxfId="9"/>
-    <tableColumn id="2" name="Mês"/>
-    <tableColumn id="3" name="Corretiva não programada" dataDxfId="8" dataCellStyle="Moeda">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Faturamento Mensal" dataDxfId="10" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Ano" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Mês"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Corretiva não programada" dataDxfId="8" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="Corretiva programada" dataDxfId="7" dataCellStyle="Moeda">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Corretiva programada" dataDxfId="7" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="Preventiva" dataDxfId="6" dataCellStyle="Moeda">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Preventiva" dataDxfId="6" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="Preditiva" dataDxfId="5" dataCellStyle="Moeda">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Preditiva" dataDxfId="5" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="Melhoria de Máquinas" dataDxfId="4" dataCellStyle="Moeda">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Melhoria de Máquinas" dataDxfId="4" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="0,5% do Faturamento Bruto Mensal" dataDxfId="3" dataCellStyle="Moeda">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="0,5% do Faturamento Bruto Mensal" dataDxfId="3" dataCellStyle="Moeda">
       <calculatedColumnFormula>A12*$G$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" name="Total Geral" dataDxfId="2" dataCellStyle="Moeda">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Total Geral" dataDxfId="2" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16535,14 +16977,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela54" displayName="Tabela54" ref="B2:D7" totalsRowShown="0">
-  <autoFilter ref="B2:D7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabela54" displayName="Tabela54" ref="B2:D7" totalsRowShown="0">
+  <autoFilter ref="B2:D7" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Tipo de manutenção"/>
-    <tableColumn id="2" name="Custo Total por tipo de manutenção (R$)" dataDxfId="1" dataCellStyle="Moeda">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Tipo de manutenção"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Custo Total por tipo de manutenção (R$)" dataDxfId="1" dataCellStyle="Moeda">
       <calculatedColumnFormula>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela54[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2026'!$D$1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Percentual de custo total por tipo" dataDxfId="0" dataCellStyle="Porcentagem">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Percentual de custo total por tipo" dataDxfId="0" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16834,88 +17276,88 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.42578125" style="35" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="12.33203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.44140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.33203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
         <v>51</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="13">
         <v>45682.625</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E2" s="17" t="str">
+      <c r="E2" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="2">
@@ -16924,40 +17366,40 @@
       <c r="J2" s="2">
         <v>0</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>9</v>
       </c>
-      <c r="L2" s="19">
+      <c r="L2" s="16">
         <f t="shared" ref="L2:L43" si="0">I2+J2</f>
         <v>350</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
         <v>55</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="13">
         <v>45705.416666666664</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E3" s="17" t="str">
+      <c r="E3" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="2">
@@ -16966,40 +17408,40 @@
       <c r="J3" s="2">
         <v>0</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>66</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="16">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
         <v>58</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <v>45736.572916666664</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E4" s="17" t="str">
+      <c r="E4" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="2">
@@ -17008,40 +17450,40 @@
       <c r="J4" s="2">
         <v>0</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>38.000000000058208</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="16">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
         <v>59</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="13">
         <v>45737.5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E5" s="17" t="str">
+      <c r="E5" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="2">
@@ -17050,40 +17492,40 @@
       <c r="J5" s="2">
         <v>0</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>20.000000000058208</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
         <v>61</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="13">
         <v>45731.510416666664</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <v>45733.052083333336</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="2">
@@ -17092,40 +17534,40 @@
       <c r="J6" s="2">
         <v>433.23</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>37.000000000116415</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="16">
         <f t="shared" si="0"/>
         <v>1333.23</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="17">
         <v>64</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="13">
         <v>45791.697916666664</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E7" s="17" t="str">
+      <c r="E7" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Maio</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="2">
@@ -17134,670 +17576,670 @@
       <c r="J7" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>7.0000000001164153</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="16">
         <f t="shared" si="0"/>
         <v>2250</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="17">
         <v>100</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="13">
         <v>45979.333333333336</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <v>45980.458333333336</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E8" s="17" t="str">
+      <c r="E8" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Novembro</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="16">
         <v>500</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="16">
         <v>0</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>27</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="16">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
         <v>102</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="13">
         <v>45979.395833333336</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <v>45999.444444444445</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E9" s="17" t="str">
+      <c r="E9" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Dezembro</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="16">
         <v>1400</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="16">
         <v>0</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>481.16666666662786</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="16">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
         <v>103</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="13">
         <v>45993.375</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <v>45999.583333333336</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E10" s="17" t="str">
+      <c r="E10" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Dezembro</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="16">
         <v>0</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="16">
         <v>0</v>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>149.00000000005821</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="20">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
         <v>104</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="13">
         <v>45992.416666666664</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <v>45992.625</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E11" s="17" t="str">
+      <c r="E11" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Dezembro</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="16">
         <v>400</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="16">
         <v>17.62</v>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>5.0000000000582077</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="16">
         <f t="shared" si="0"/>
         <v>417.62</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
         <v>106</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="13">
         <v>45999.416666666664</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <v>45999.708333333336</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E12" s="17" t="str">
+      <c r="E12" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Dezembro</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="16">
         <v>1758.2</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="16">
         <v>0</v>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>7.0000000001164153</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="16">
         <f t="shared" si="0"/>
         <v>1758.2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="17">
         <v>108</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="13">
         <v>46038.493055555555</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="13">
         <v>46043.441666666666</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E13" s="17" t="str">
+      <c r="E13" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="16">
         <v>1125</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="16">
         <v>0</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>118.76666666666279</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="16">
         <f t="shared" si="0"/>
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
         <v>109</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="13">
         <v>46042.493055555555</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="13">
         <v>46066.583333333336</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E14" s="17" t="str">
+      <c r="E14" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="16">
         <v>850</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="16">
         <v>0</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K14" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>578.16666666674428</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="16">
         <f t="shared" si="0"/>
         <v>850</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="17">
         <v>110</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="13">
         <v>46042.375</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <v>46045.458333333336</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E15" s="17" t="str">
+      <c r="E15" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="16">
         <v>945</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="16">
         <v>0</v>
       </c>
-      <c r="K15" s="20">
+      <c r="K15" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>74.000000000058208</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="16">
         <f t="shared" si="0"/>
         <v>945</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="17">
         <v>111</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="13">
         <v>46043.375</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <v>46043.631944444445</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E16" s="17" t="str">
+      <c r="E16" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="16">
         <v>900</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="16">
         <v>0</v>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>6.1666666666860692</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="16">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="17">
         <v>112</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="13">
         <v>46049.375</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="13">
         <v>46049.458333333336</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E17" s="17" t="str">
+      <c r="E17" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="16">
         <v>260</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="16">
         <v>0</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>2.0000000000582077</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="16">
         <f t="shared" si="0"/>
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="17">
         <v>113</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="13">
         <v>46056.4375</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13">
         <v>46058.666666666664</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E18" s="17" t="str">
+      <c r="E18" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="16">
         <v>800</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="16">
         <v>0</v>
       </c>
-      <c r="K18" s="20">
+      <c r="K18" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>53.499999999941792</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="16">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="20">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="17">
         <v>114</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="13">
         <v>46062.395833333336</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="13">
         <v>46064.625</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E19" s="17" t="str">
+      <c r="E19" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="H19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="16">
         <v>570</v>
       </c>
-      <c r="J19" s="19">
+      <c r="J19" s="16">
         <v>0</v>
       </c>
-      <c r="K19" s="20">
+      <c r="K19" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>53.499999999941792</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="16">
         <f t="shared" si="0"/>
         <v>570</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="17">
         <v>115</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="13">
         <v>46065.416666666664</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13">
         <v>46065.625</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E20" s="17" t="str">
+      <c r="E20" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="16">
         <v>1025</v>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="16">
         <v>0</v>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>5.0000000000582077</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="16">
         <f t="shared" si="0"/>
         <v>1025</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="17">
         <v>116</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="13">
         <v>46071.333333333336</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="13">
         <v>46072.625</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E21" s="17" t="str">
+      <c r="E21" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="16">
         <v>1000</v>
       </c>
-      <c r="J21" s="19">
+      <c r="J21" s="16">
         <v>0</v>
       </c>
-      <c r="K21" s="20">
+      <c r="K21" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>30.999999999941792</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="16">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="17">
         <v>117</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="13">
         <v>46073.441666666666</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13">
         <v>46073.666666666664</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E22" s="17" t="str">
+      <c r="E22" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="16">
         <v>600</v>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="16">
         <v>0</v>
       </c>
-      <c r="K22" s="20">
+      <c r="K22" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>5.3999999999650754</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="16">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="13">
         <v>45658.333333333336</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E23" s="17" t="str">
+      <c r="E23" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="23" t="s">
+      <c r="H23" t="s">
         <v>7</v>
       </c>
       <c r="I23" s="2">
@@ -17806,40 +18248,40 @@
       <c r="J23" s="2">
         <v>0</v>
       </c>
-      <c r="K23" s="20">
+      <c r="K23" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="16">
         <f t="shared" si="0"/>
         <v>3850</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="13">
         <v>45689.333333333336</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E24" s="17" t="str">
+      <c r="E24" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" t="s">
         <v>7</v>
       </c>
       <c r="I24" s="2">
@@ -17848,40 +18290,40 @@
       <c r="J24" s="2">
         <v>0</v>
       </c>
-      <c r="K24" s="20">
+      <c r="K24" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="16">
         <f t="shared" si="0"/>
         <v>3167</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="13">
         <v>45697.604166666664</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E25" s="17" t="str">
+      <c r="E25" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="23" t="s">
+      <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="2">
@@ -17890,40 +18332,40 @@
       <c r="J25" s="2">
         <v>0</v>
       </c>
-      <c r="K25" s="20">
+      <c r="K25" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>36</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="16">
         <f t="shared" si="0"/>
         <v>983</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="13">
         <v>45717.333333333336</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E26" s="17" t="str">
+      <c r="E26" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" t="s">
         <v>46</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" t="s">
         <v>7</v>
       </c>
       <c r="I26" s="2">
@@ -17932,40 +18374,40 @@
       <c r="J26" s="2">
         <v>0</v>
       </c>
-      <c r="K26" s="20">
+      <c r="K26" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="16">
         <f t="shared" si="0"/>
         <v>2700</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <v>45719.510416666664</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E27" s="17" t="str">
+      <c r="E27" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" t="s">
         <v>22</v>
       </c>
       <c r="I27" s="2">
@@ -17974,40 +18416,40 @@
       <c r="J27" s="2">
         <v>0</v>
       </c>
-      <c r="K27" s="20">
+      <c r="K27" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>11.000000000058208</v>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="13">
         <v>45748.333333333336</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E28" s="17" t="str">
+      <c r="E28" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Abril</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" t="s">
         <v>46</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="G28" t="s">
         <v>46</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H28" t="s">
         <v>7</v>
       </c>
       <c r="I28" s="2">
@@ -18016,40 +18458,40 @@
       <c r="J28" s="2">
         <v>0</v>
       </c>
-      <c r="K28" s="20">
+      <c r="K28" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="16">
         <f t="shared" si="0"/>
         <v>2775</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="13">
         <v>45759.65625</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E29" s="17" t="str">
+      <c r="E29" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Abril</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" t="s">
         <v>90</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" t="s">
         <v>19</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="H29" t="s">
         <v>23</v>
       </c>
       <c r="I29" s="2">
@@ -18058,40 +18500,40 @@
       <c r="J29" s="2">
         <v>101.72</v>
       </c>
-      <c r="K29" s="20">
+      <c r="K29" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>15.999999999941792</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="16">
         <f t="shared" si="0"/>
         <v>626.72</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="13">
         <v>45778.333333333336</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E30" s="17" t="str">
+      <c r="E30" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Maio</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" t="s">
         <v>46</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" t="s">
         <v>46</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" t="s">
         <v>7</v>
       </c>
       <c r="I30" s="2">
@@ -18100,40 +18542,40 @@
       <c r="J30" s="2">
         <v>0</v>
       </c>
-      <c r="K30" s="20">
+      <c r="K30" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="16">
         <f t="shared" si="0"/>
         <v>3687</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="13">
         <v>45780.635416666664</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E31" s="17" t="str">
+      <c r="E31" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Maio</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="G31" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" s="2">
@@ -18142,732 +18584,732 @@
       <c r="J31" s="2">
         <v>270.64999999999998</v>
       </c>
-      <c r="K31" s="20">
+      <c r="K31" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>70.000000000116415</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="16">
         <f t="shared" si="0"/>
         <v>570.65</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="13">
         <v>45785.635416666664</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="13">
         <v>45785.6875</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E32" s="17" t="str">
+      <c r="E32" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Maio</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H32" s="18" t="s">
+      <c r="H32" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="16">
         <v>400</v>
       </c>
-      <c r="J32" s="19">
+      <c r="J32" s="16">
         <v>155</v>
       </c>
-      <c r="K32" s="20">
+      <c r="K32" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>1.2500000000582077</v>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="16">
         <f t="shared" si="0"/>
         <v>555</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="13">
         <v>45809.333333333336</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="13">
         <v>45810.708333333336</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E33" s="17" t="str">
+      <c r="E33" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Junho</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H33" s="18" t="s">
+      <c r="H33" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="16">
         <v>4200</v>
       </c>
-      <c r="J33" s="19">
+      <c r="J33" s="16">
         <v>0</v>
       </c>
-      <c r="K33" s="20">
+      <c r="K33" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="16">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="13">
         <v>45809.333333333336</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="13">
         <v>45810.708333333336</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E34" s="17" t="str">
+      <c r="E34" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Junho</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="H34" s="18" t="s">
+      <c r="H34" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="16">
         <v>503.03</v>
       </c>
-      <c r="J34" s="19">
+      <c r="J34" s="16">
         <v>0</v>
       </c>
-      <c r="K34" s="20">
+      <c r="K34" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="16">
         <f t="shared" si="0"/>
         <v>503.03</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="13">
         <v>45839.333333333336</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="13">
         <v>45840.708333333336</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E35" s="17" t="str">
+      <c r="E35" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Julho</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="16">
         <v>4200</v>
       </c>
-      <c r="J35" s="19">
+      <c r="J35" s="16">
         <v>0</v>
       </c>
-      <c r="K35" s="20">
+      <c r="K35" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>33</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="16">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="13">
         <v>45870.291666666664</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="13">
         <v>45871.708333333336</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E36" s="17" t="str">
+      <c r="E36" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Agosto</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="H36" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="16">
         <v>2100</v>
       </c>
-      <c r="J36" s="19">
+      <c r="J36" s="16">
         <v>0</v>
       </c>
-      <c r="K36" s="20">
+      <c r="K36" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>34.000000000116415</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="16">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="13">
         <v>45875.416666666664</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="13">
         <v>45876.583333333336</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E37" s="17" t="str">
+      <c r="E37" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Agosto</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H37" s="18" t="s">
+      <c r="H37" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="16">
         <v>2372.14</v>
       </c>
-      <c r="J37" s="19">
+      <c r="J37" s="16">
         <v>0</v>
       </c>
-      <c r="K37" s="20">
+      <c r="K37" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>28.000000000116415</v>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="16">
         <f t="shared" si="0"/>
         <v>2372.14</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="13">
         <v>45901.291666666664</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="13">
         <v>45902.708333333336</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E38" s="17" t="str">
+      <c r="E38" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Setembro</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H38" s="18" t="s">
+      <c r="H38" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="16">
         <v>1200</v>
       </c>
-      <c r="J38" s="19">
+      <c r="J38" s="16">
         <v>0</v>
       </c>
-      <c r="K38" s="20">
+      <c r="K38" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>34.000000000116415</v>
       </c>
-      <c r="L38" s="19">
+      <c r="L38" s="16">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="13">
         <v>45918.416666666664</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="13">
         <v>45918.583333333336</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E39" s="17" t="str">
+      <c r="E39" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Setembro</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="16">
         <v>300</v>
       </c>
-      <c r="J39" s="19">
+      <c r="J39" s="16">
         <v>0</v>
       </c>
-      <c r="K39" s="20">
+      <c r="K39" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>4.0000000001164153</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="16">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="20" t="s">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="13">
         <v>45923.364583333336</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="13">
         <v>45923.493055555555</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E40" s="17" t="str">
+      <c r="E40" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Setembro</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="H40" s="18" t="s">
+      <c r="H40" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="16">
         <v>976.67</v>
       </c>
-      <c r="J40" s="19">
+      <c r="J40" s="16">
         <v>0</v>
       </c>
-      <c r="K40" s="20">
+      <c r="K40" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>3.0833333332557231</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="16">
         <f t="shared" si="0"/>
         <v>976.67</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="13">
         <v>45931.291666666664</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="13">
         <v>45932.708333333336</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E41" s="17" t="str">
+      <c r="E41" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Outubro</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="18" t="s">
+      <c r="H41" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="16">
         <v>950</v>
       </c>
-      <c r="J41" s="19">
+      <c r="J41" s="16">
         <v>0</v>
       </c>
-      <c r="K41" s="20">
+      <c r="K41" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>34.000000000116415</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="16">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="13">
         <v>45946.375</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="13">
         <v>45947.416666666664</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E42" s="17" t="str">
+      <c r="E42" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Outubro</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="18" t="s">
+      <c r="H42" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="16">
         <v>2372.13</v>
       </c>
-      <c r="J42" s="19">
+      <c r="J42" s="16">
         <v>0</v>
       </c>
-      <c r="K42" s="20">
+      <c r="K42" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>24.999999999941792</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="16">
         <f t="shared" si="0"/>
         <v>2372.13</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="13">
         <v>45988.395833333336</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="13">
         <v>45988.583333333336</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2025</v>
       </c>
-      <c r="E43" s="17" t="str">
+      <c r="E43" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Novembro</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G43" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="18" t="s">
+      <c r="H43" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="16">
         <v>1475</v>
       </c>
-      <c r="J43" s="19">
+      <c r="J43" s="16">
         <v>300</v>
       </c>
-      <c r="K43" s="20">
+      <c r="K43" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>4.5</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="16">
         <f t="shared" si="0"/>
         <v>1775</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="20">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="17">
         <v>119</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="13">
         <v>46087.680555555555</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="13">
         <v>46098.666666666664</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E44" s="17" t="str">
+      <c r="E44" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="18" t="s">
+      <c r="G44" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H44" s="18" t="s">
+      <c r="H44" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="16">
         <f>937+1399.99</f>
         <v>2336.9899999999998</v>
       </c>
-      <c r="J44" s="19">
+      <c r="J44" s="16">
         <v>6200</v>
       </c>
-      <c r="K44" s="20">
+      <c r="K44" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>263.66666666662786</v>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="16">
         <f>I44+J44</f>
         <v>8536.99</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="20">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="17">
         <v>120</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="13">
         <v>46066.541666666664</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="13">
         <v>46113.666666666664</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E45" s="17" t="str">
+      <c r="E45" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Abril</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H45" s="18" t="s">
+      <c r="H45" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="20">
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>1131</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="16">
         <f>I45+J45</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="17">
         <v>121</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="13">
         <v>46108.541666666664</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="13">
         <v>46108.625</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E46" s="17" t="str">
+      <c r="E46" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G46" s="18" t="s">
+      <c r="G46" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H46" s="18" t="s">
+      <c r="H46" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="16">
         <v>0</v>
       </c>
-      <c r="J46" s="19">
+      <c r="J46" s="16">
         <v>23</v>
       </c>
-      <c r="K46" s="20">
+      <c r="K46" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>2.0000000000582077</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="16">
         <f>I46+J46</f>
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="20">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="17">
         <v>122</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="13">
         <v>46077.541666666664</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="13">
         <v>46082.541666666664</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E47" s="17" t="str">
+      <c r="E47" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="H47" s="18" t="s">
+      <c r="H47" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I47" s="19">
+      <c r="I47" s="16">
         <v>0</v>
       </c>
-      <c r="J47" s="19">
+      <c r="J47" s="16">
         <v>1916.23</v>
       </c>
-      <c r="K47" s="20">
+      <c r="K47" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>120</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="16">
         <f>I47+J47</f>
         <v>1916.23</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="20">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="17">
         <v>107</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="13">
         <v>46097.541666666664</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="13">
         <v>46097.625</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="14">
         <f>YEAR(Tabela1[[#This Row],[Data de Fechamento]])</f>
         <v>2026</v>
       </c>
-      <c r="E48" s="17" t="str">
+      <c r="E48" s="15" t="str">
         <f>PROPER(TEXT(Tabela1[[#This Row],[Data de Fechamento]],"mmmm"))</f>
         <v>Março</v>
       </c>
-      <c r="F48" s="18" t="s">
+      <c r="F48" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G48" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="H48" s="18" t="s">
+      <c r="H48" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I48" s="19">
+      <c r="I48" s="16">
         <v>0</v>
       </c>
-      <c r="J48" s="19">
+      <c r="J48" s="16">
         <v>460</v>
       </c>
-      <c r="K48" s="20">
+      <c r="K48" s="17">
         <f>(Tabela1[[#This Row],[Data de Fechamento]]-Tabela1[[#This Row],[Data de Abertura]])*24</f>
         <v>2.0000000000582077</v>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="16">
         <f>I48+J48</f>
         <v>460</v>
       </c>
     </row>
-    <row r="49" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L49" s="40"/>
+    <row r="49" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L49" s="35"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H48">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Corretiva programada,Corretiva não programada,Preventiva,Preditiva,Melhoria de máquinas"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18879,50 +19321,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" customWidth="1"/>
     <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+    <row r="1" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="25">
+      <c r="C1" s="36"/>
+      <c r="D1" s="21">
         <v>2025</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="33">
+      <c r="G1" s="28">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -18930,13 +19372,13 @@
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela5[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2025'!$D$1)</f>
         <v>8507.5299999999988</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f>Tabela5[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela5[Custo Total por tipo de manutenção (R$)])</f>
         <v>0.17497144833892367</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>23</v>
       </c>
@@ -18944,13 +19386,13 @@
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela5[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2025'!$D$1)</f>
         <v>11285.86</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f>Tabela5[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela5[Custo Total por tipo de manutenção (R$)])</f>
         <v>0.23211240747318262</v>
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -18958,13 +19400,13 @@
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela5[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2025'!$D$1)</f>
         <v>28829</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f>Tabela5[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela5[Custo Total por tipo de manutenção (R$)])</f>
         <v>0.59291614418789373</v>
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -18972,13 +19414,13 @@
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela5[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2025'!$D$1)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f>Tabela5[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela5[Custo Total por tipo de manutenção (R$)])</f>
         <v>0</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -18986,70 +19428,70 @@
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela5[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2025'!$D$1)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f>Tabela5[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela5[Custo Total por tipo de manutenção (R$)])</f>
         <v>0</v>
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D8" s="21">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D8" s="18">
         <f>SUM(D3:D7)</f>
         <v>1</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="23">
         <f>H19-J23</f>
         <v>-3575.8199999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+    <row r="10" spans="1:11" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
     </row>
-    <row r="11" spans="1:11" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>801322.87</v>
       </c>
@@ -19059,27 +19501,27 @@
       <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</f>
         <v>350</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</f>
         <v>3850</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>4006.6143500000003</v>
       </c>
@@ -19089,7 +19531,7 @@
       </c>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>1311185.73</v>
       </c>
@@ -19099,27 +19541,27 @@
       <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B13)</f>
         <v>1033</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B13)</f>
         <v>3167</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>6555.9286499999998</v>
       </c>
@@ -19129,7 +19571,7 @@
       </c>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>1030344.22</v>
       </c>
@@ -19139,27 +19581,27 @@
       <c r="C14" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B14)</f>
         <v>1533.23</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B14)</f>
         <v>500</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B14)</f>
         <v>2700</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>5151.7210999999998</v>
       </c>
@@ -19169,7 +19611,7 @@
       </c>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>761326.55</v>
       </c>
@@ -19179,27 +19621,27 @@
       <c r="C15" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B15)</f>
         <v>626.72</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B15)</f>
         <v>2775</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>3806.6327500000002</v>
       </c>
@@ -19209,7 +19651,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>1605718.99</v>
       </c>
@@ -19219,27 +19661,27 @@
       <c r="C16" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B16)</f>
         <v>2820.65</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B16)</f>
         <v>555</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B16)</f>
         <v>3687</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>8028.5949499999997</v>
       </c>
@@ -19249,7 +19691,7 @@
       </c>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>1219442.79</v>
       </c>
@@ -19279,7 +19721,7 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C17,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>6097.2139500000003</v>
       </c>
@@ -19289,7 +19731,7 @@
       </c>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>886919.59000000008</v>
       </c>
@@ -19319,7 +19761,7 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C18,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>4434.5979500000003</v>
       </c>
@@ -19329,7 +19771,7 @@
       </c>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>836445.73999999987</v>
       </c>
@@ -19359,7 +19801,7 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C19,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B19)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>4182.2286999999997</v>
       </c>
@@ -19369,7 +19811,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>635862.29</v>
       </c>
@@ -19399,7 +19841,7 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C20,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B20)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>3179.3114500000001</v>
       </c>
@@ -19409,7 +19851,7 @@
       </c>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>753559.98</v>
       </c>
@@ -19439,7 +19881,7 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C21,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B21)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>3767.7999</v>
       </c>
@@ -19449,7 +19891,7 @@
       </c>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>518347.47</v>
       </c>
@@ -19479,7 +19921,7 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C22,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B22)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>2591.7373499999999</v>
       </c>
@@ -19489,7 +19931,7 @@
       </c>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>776659.91</v>
       </c>
@@ -19519,7 +19961,7 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2025'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2025'!$C23,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2025'!$B23)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="20">
         <f>Tabela4[[#This Row],[Faturemento Mensal]]*$G$1</f>
         <v>3883.2995500000002</v>
       </c>
@@ -19547,386 +19989,386 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>2025</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>40012.11</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>21650.48</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>43775</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4">
         <v>60000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>5992.48</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>2976.1000000000004</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>4200</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>5000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>6150.51</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>2288.54</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>4200</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>3431.61</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>1863.39</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>4200</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7">
         <v>5000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>5788.41</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>690.45</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>4200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8">
         <v>5000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>7191.1100000000006</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>4200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9">
         <v>5000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>503.03</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10">
         <v>4200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10">
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11">
         <v>0</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11">
         <v>4200</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11">
         <v>5000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12">
         <v>2372.14</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12">
         <v>4200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12">
         <v>5000</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>1276.67</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13">
         <v>2372.13</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13">
         <v>4200</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13">
         <v>5000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>976.67</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14">
         <v>2372.13</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14">
         <v>4200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>500</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15">
         <v>4007.3999999999996</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15">
         <v>1775</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15">
         <v>5000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>8201.619999999999</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16">
         <v>2708.2</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16">
         <v>0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16">
         <v>5000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
         <v>2026</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>8358.2000000000007</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17">
         <v>7683</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17">
         <v>0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17">
         <v>10000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <v>6558.2</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18">
         <v>2758</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18">
         <v>0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18">
         <v>5000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>1800</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19">
         <v>4925</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19">
         <v>0</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19">
         <v>5000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <v>48370.31</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20">
         <v>29333.48</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20">
         <v>43775</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20">
         <v>70000</v>
       </c>
     </row>
@@ -19937,11 +20379,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="16384" width="9.109375" style="7"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -19951,203 +20393,202 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="24.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="23" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="26" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" customWidth="1"/>
+    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+    <row r="1" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="39">
+      <c r="C1" s="36"/>
+      <c r="D1" s="34">
         <v>2026</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="33">
+      <c r="G1" s="28">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="33" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="2">
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela54[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2026'!$D$1)</f>
         <v>14606.22</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
         <v>0.79333254395960717</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="2">
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela54[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2026'!$D$1)</f>
         <v>3805</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
         <v>0.20666745604039274</v>
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2">
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela54[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2026'!$D$1)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
         <v>0</v>
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2">
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela54[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2026'!$D$1)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
         <v>0</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="2">
         <f>SUMIFS(Dados_OS!L:L,Dados_OS!H:H,Tabela54[[#This Row],[Tipo de manutenção]],Dados_OS!D:D,'Tratamento de Dados 2026'!$D$1)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
         <v>0</v>
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D8" s="21">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D8" s="18">
         <f>SUM(D3:D7)</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="9" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+    <row r="10" spans="1:11" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
     </row>
-    <row r="11" spans="1:11" s="9" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
+    <row r="11" spans="1:11" s="3" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30">
+    <row r="12" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25">
         <v>647585.69999999995</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="32">
         <v>2026</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</f>
         <v>2330</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</f>
         <v>900</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C12,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="20">
         <f t="shared" ref="I12:I23" si="0">A12*$G$1</f>
         <v>3237.9285</v>
       </c>
@@ -20155,39 +20596,39 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>3230</v>
       </c>
-      <c r="K12" s="28"/>
+      <c r="K12" s="24"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="31">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
         <v>844687.4</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="32">
         <v>2026</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B13)</f>
         <v>1800</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B13)</f>
         <v>2445</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C13,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B13)</f>
         <v>600</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="20">
         <f t="shared" si="0"/>
         <v>4223.4369999999999</v>
       </c>
@@ -20195,39 +20636,39 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>4845</v>
       </c>
-      <c r="K13" s="28"/>
+      <c r="K13" s="24"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="25">
         <v>753982.97</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="32">
         <v>2026</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B14)</f>
         <v>10476.219999999999</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B14)</f>
         <v>460</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C14,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="20">
         <f t="shared" si="0"/>
         <v>3769.9148500000001</v>
       </c>
@@ -20235,39 +20676,39 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>10936.22</v>
       </c>
-      <c r="K14" s="28"/>
+      <c r="K14" s="24"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="26">
         <v>0</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="32">
         <v>2026</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C15,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20275,39 +20716,39 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K15" s="28"/>
+      <c r="K15" s="24"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="25">
         <v>0</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="32">
         <v>2026</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C16,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20315,19 +20756,19 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K16" s="28"/>
+      <c r="K16" s="24"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="31">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="26">
         <v>0</v>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="32">
         <v>2026</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C17,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B17)</f>
         <v>0</v>
       </c>
@@ -20335,19 +20776,19 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C17,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C17,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C17,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C17,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20355,19 +20796,19 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K17" s="28"/>
+      <c r="K17" s="24"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="25">
         <v>0</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="32">
         <v>2026</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C18,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B18)</f>
         <v>0</v>
       </c>
@@ -20375,19 +20816,19 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C18,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B18)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C18,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C18,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C18,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20395,19 +20836,19 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K18" s="28"/>
+      <c r="K18" s="24"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="26">
         <v>0</v>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="32">
         <v>2026</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C19,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B19)</f>
         <v>0</v>
       </c>
@@ -20415,19 +20856,19 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C19,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B19)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C19,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B19)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C19,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B19)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C19,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B19)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20435,19 +20876,19 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K19" s="28"/>
+      <c r="K19" s="24"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="25">
         <v>0</v>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="32">
         <v>2026</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C20,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B20)</f>
         <v>0</v>
       </c>
@@ -20455,19 +20896,19 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C20,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C20,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B20)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C20,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B20)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C20,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B20)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20475,19 +20916,19 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K20" s="28"/>
+      <c r="K20" s="24"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="31">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="26">
         <v>0</v>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="32">
         <v>2026</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C21,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B21)</f>
         <v>0</v>
       </c>
@@ -20495,19 +20936,19 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C21,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B21)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C21,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B21)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C21,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B21)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C21,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B21)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20515,19 +20956,19 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K21" s="28"/>
+      <c r="K21" s="24"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="25">
         <v>0</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="32">
         <v>2026</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C22,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B22)</f>
         <v>0</v>
       </c>
@@ -20535,19 +20976,19 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C22,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C22,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C22,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B22)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C22,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B22)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20555,19 +20996,19 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K22" s="28"/>
+      <c r="K22" s="24"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="31">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="26">
         <v>0</v>
       </c>
-      <c r="B23" s="37">
+      <c r="B23" s="32">
         <v>2026</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!D$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C23,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B23)</f>
         <v>0</v>
       </c>
@@ -20575,19 +21016,19 @@
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!E$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C23,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B23)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!F$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C23,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B23)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="19">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!G$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C23,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B23)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="29">
         <f>SUMIFS(Tabela1[[Custo_Total]:[Custo_Total]],Tabela1[[Tipo_Manutencao]:[Tipo_Manutencao]],'Tratamento de Dados 2026'!H$11,Tabela1[[Mês Fechamento]:[Mês Fechamento]],'Tratamento de Dados 2026'!$C23,Tabela1[[Ano]:[Ano]],'Tratamento de Dados 2026'!$B23)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20595,14 +21036,11 @@
         <f>SUM(Tabela43[[#This Row],[Corretiva não programada]:[Melhoria de Máquinas]])</f>
         <v>0</v>
       </c>
-      <c r="K23" s="28"/>
+      <c r="K23" s="24"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H24" s="29"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -20619,11 +21057,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="16384" width="9.109375" style="7"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2495ADD-2524-40D8-BEF9-CAFA197D1027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF1B296-0C12-40D8-9311-1A7F2F3FC394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,18 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>Preventiva</t>
   </si>
   <si>
-    <t>Resumo de Custos por Tipo de Manutenção</t>
-  </si>
-  <si>
     <t>Preditiva</t>
-  </si>
-  <si>
-    <t>Melhoria</t>
   </si>
   <si>
     <t>Corretiva não programada</t>
@@ -85,15 +79,6 @@
   </si>
   <si>
     <t>Dezembro</t>
-  </si>
-  <si>
-    <t>Custo Total por tipo de manutenção (R$)</t>
-  </si>
-  <si>
-    <t>Tipo de manutenção</t>
-  </si>
-  <si>
-    <t>Percentual de custo total por tipo</t>
   </si>
   <si>
     <t>Ano</t>
@@ -137,9 +122,6 @@
   <si>
     <t>Faturamento Mensal</t>
   </si>
-  <si>
-    <t>Meta</t>
-  </si>
 </sst>
 </file>
 
@@ -149,7 +131,14 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,62 +151,15 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -232,27 +174,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF00B050"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF00B050"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF00B050"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF00B050"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -271,17 +198,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -289,75 +211,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
-    <cellStyle name="Vírgula" xfId="3" builtinId="3"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6215,22 +6085,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabela54" displayName="Tabela54" ref="B2:D7" totalsRowShown="0">
-  <autoFilter ref="B2:D7" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Tipo de manutenção"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Custo Total por tipo de manutenção (R$)" dataDxfId="1" dataCellStyle="Moeda">
-      <calculatedColumnFormula>SUMIFS(#REF!,#REF!,Tabela54[[#This Row],[Tipo de manutenção]],#REF!,'Tratamento de Dados 2026'!$D$1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Percentual de custo total por tipo" dataDxfId="0" dataCellStyle="Porcentagem">
-      <calculatedColumnFormula>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6539,27 +6393,27 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="2">
         <v>2025</v>
       </c>
       <c r="B4">
@@ -6579,8 +6433,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>7</v>
+      <c r="A5" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="B5">
         <v>5992.48</v>
@@ -6599,8 +6453,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>8</v>
+      <c r="A6" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B6">
         <v>6150.51</v>
@@ -6619,8 +6473,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>27</v>
+      <c r="A7" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B7">
         <v>3431.61</v>
@@ -6639,8 +6493,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>28</v>
+      <c r="A8" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B8">
         <v>5788.41</v>
@@ -6659,8 +6513,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>29</v>
+      <c r="A9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
         <v>7191.1100000000006</v>
@@ -6679,8 +6533,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
+      <c r="A10" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="B10">
         <v>503.03</v>
@@ -6699,8 +6553,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>10</v>
+      <c r="A11" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6719,8 +6573,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>11</v>
+      <c r="A12" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6739,8 +6593,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>12</v>
+      <c r="A13" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B13">
         <v>1276.67</v>
@@ -6759,8 +6613,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>13</v>
+      <c r="A14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B14">
         <v>976.67</v>
@@ -6779,8 +6633,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>14</v>
+      <c r="A15" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B15">
         <v>500</v>
@@ -6799,8 +6653,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>15</v>
+      <c r="A16" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="B16">
         <v>8201.619999999999</v>
@@ -6819,7 +6673,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="2">
         <v>2026</v>
       </c>
       <c r="B17">
@@ -6839,8 +6693,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>7</v>
+      <c r="A18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="B18">
         <v>6558.2</v>
@@ -6859,8 +6713,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>8</v>
+      <c r="A19" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B19">
         <v>1800</v>
@@ -6879,8 +6733,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
+      <c r="A20" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B20">
         <v>48370.31</v>
@@ -6906,7 +6760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -6922,244 +6776,136 @@
     <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="11">
-        <v>2026</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="9">
-        <v>5.0000000000000001E-3</v>
+      <c r="H1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>18</v>
+      <c r="A2" s="8">
+        <v>647585.69999999995</v>
+      </c>
+      <c r="B2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8">
+        <v>2330</v>
+      </c>
+      <c r="E2" s="8">
+        <v>900</v>
+      </c>
+      <c r="F2" s="8">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8">
+        <v>3237.9285</v>
+      </c>
+      <c r="J2" s="8">
+        <v>3230</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="e">
-        <f>SUMIFS(#REF!,#REF!,Tabela54[[#This Row],[Tipo de manutenção]],#REF!,'Tratamento de Dados 2026'!$D$1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D3" s="3" t="e">
-        <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="2"/>
+      <c r="A3" s="8">
+        <v>844687.4</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1800</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2445</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8">
+        <v>600</v>
+      </c>
+      <c r="I3" s="8">
+        <v>4223.4369999999999</v>
+      </c>
+      <c r="J3" s="8">
+        <v>4845</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="e">
-        <f>SUMIFS(#REF!,#REF!,Tabela54[[#This Row],[Tipo de manutenção]],#REF!,'Tratamento de Dados 2026'!$D$1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D4" s="3" t="e">
-        <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="A4" s="8">
+        <v>753982.97</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="8">
+        <v>10476.219999999999</v>
+      </c>
+      <c r="E4" s="8">
+        <v>460</v>
+      </c>
+      <c r="F4" s="8">
         <v>0</v>
       </c>
-      <c r="C5" s="2" t="e">
-        <f>SUMIFS(#REF!,#REF!,Tabela54[[#This Row],[Tipo de manutenção]],#REF!,'Tratamento de Dados 2026'!$D$1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D5" s="3" t="e">
-        <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="e">
-        <f>SUMIFS(#REF!,#REF!,Tabela54[[#This Row],[Tipo de manutenção]],#REF!,'Tratamento de Dados 2026'!$D$1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D6" s="3" t="e">
-        <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="e">
-        <f>SUMIFS(#REF!,#REF!,Tabela54[[#This Row],[Tipo de manutenção]],#REF!,'Tratamento de Dados 2026'!$D$1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D7" s="3" t="e">
-        <f>Tabela54[[#This Row],[Custo Total por tipo de manutenção (R$)]]/SUM(Tabela54[Custo Total por tipo de manutenção (R$)])</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D8" s="7" t="e">
-        <f>SUM(D3:D7)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="14" t="s">
+      <c r="G4" s="8">
         <v>0</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
-        <v>647585.69999999995</v>
-      </c>
-      <c r="B11" s="15">
-        <v>2026</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="17">
-        <v>2330</v>
-      </c>
-      <c r="E11" s="17">
-        <v>900</v>
-      </c>
-      <c r="F11" s="17">
+      <c r="H4" s="8">
         <v>0</v>
       </c>
-      <c r="G11" s="17">
-        <v>0</v>
-      </c>
-      <c r="H11" s="17">
-        <v>0</v>
-      </c>
-      <c r="I11" s="17">
-        <v>3237.9285</v>
-      </c>
-      <c r="J11" s="17">
-        <v>3230</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
-        <v>844687.4</v>
-      </c>
-      <c r="B12" s="15">
-        <v>2026</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="17">
-        <v>1800</v>
-      </c>
-      <c r="E12" s="17">
-        <v>2445</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>600</v>
-      </c>
-      <c r="I12" s="17">
-        <v>4223.4369999999999</v>
-      </c>
-      <c r="J12" s="17">
-        <v>4845</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
-        <v>753982.97</v>
-      </c>
-      <c r="B13" s="15">
-        <v>2026</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="17">
-        <v>10476.219999999999</v>
-      </c>
-      <c r="E13" s="17">
-        <v>460</v>
-      </c>
-      <c r="F13" s="17">
-        <v>0</v>
-      </c>
-      <c r="G13" s="17">
-        <v>0</v>
-      </c>
-      <c r="H13" s="17">
-        <v>0</v>
-      </c>
-      <c r="I13" s="17">
+      <c r="I4" s="8">
         <v>3769.9148500000001</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J4" s="8">
         <v>10936.22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF1B296-0C12-40D8-9311-1A7F2F3FC394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35259B3D-A752-499F-BE03-9D8AD406840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6764,13 +6764,13 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" customWidth="1"/>
-    <col min="7" max="7" width="22.5546875" customWidth="1"/>
-    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" customWidth="1"/>
     <col min="9" max="9" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35259B3D-A752-499F-BE03-9D8AD406840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C33D6D2-21F1-4974-9FD9-8076BA6A38A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C33D6D2-21F1-4974-9FD9-8076BA6A38A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D64246B9-D6B1-484B-9B55-AB4F51B61B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5614,7 +5614,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Manutencao" refreshedDate="46078.332756481483" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="14" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B11:I23" sheet="Tratamento de Dados 2025"/>
+    <worksheetSource ref="B11:I23" sheet="Tratamento de Dados 2025" r:id="rId2"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="Ano" numFmtId="0">

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D64246B9-D6B1-484B-9B55-AB4F51B61B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E50FA1-1D4F-4C60-91D0-FB1D715910F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -202,7 +202,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -222,6 +222,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6824,13 +6825,13 @@
       <c r="E2" s="8">
         <v>900</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>0</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="9">
         <v>0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="9">
         <v>0</v>
       </c>
       <c r="I2" s="8">
@@ -6856,10 +6857,10 @@
       <c r="E3" s="8">
         <v>2445</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="9">
         <v>0</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="9">
         <v>0</v>
       </c>
       <c r="H3" s="8">
@@ -6888,13 +6889,13 @@
       <c r="E4" s="8">
         <v>460</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="9">
         <v>0</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="9">
         <v>0</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="9">
         <v>0</v>
       </c>
       <c r="I4" s="8">

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8e481a7cc57d7010/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E50FA1-1D4F-4C60-91D0-FB1D715910F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{63E50FA1-1D4F-4C60-91D0-FB1D715910F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F627121E-AFF4-471D-8870-661D9E006ABC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6852,7 +6852,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="8">
-        <v>1800</v>
+        <v>1800.05</v>
       </c>
       <c r="E3" s="8">
         <v>2445</v>
@@ -6884,7 +6884,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="8">
-        <v>10476.219999999999</v>
+        <v>10476.200000000001</v>
       </c>
       <c r="E4" s="8">
         <v>460</v>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F63FBA96-B9C8-4318-8219-531E01482539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEDF75D-6601-42CE-B119-76A2ED61FA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FA4A0903-8A5F-40BA-8712-46AAF48B56BA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Faturamento Mensal</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Março</t>
+  </si>
+  <si>
+    <t>Abril</t>
   </si>
 </sst>
 </file>
@@ -507,13 +510,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73D102E3-B151-45B0-865D-C9907B87806D}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,6 +643,28 @@
       <c r="J4" s="4">
         <v>10936.22</v>
       </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manutencao\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEDF75D-6601-42CE-B119-76A2ED61FA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FA4A0903-8A5F-40BA-8712-46AAF48B56BA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -86,11 +85,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,7 +160,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -175,6 +174,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,14 +509,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73D102E3-B151-45B0-865D-C9907B87806D}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="10" width="12.5546875" customWidth="1"/>
+    <col min="1" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="42.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,7 +548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>647585.69999999995</v>
       </c>
@@ -580,7 +580,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>844687.4</v>
       </c>
@@ -612,7 +612,7 @@
         <v>4845</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>753982.97</v>
       </c>
@@ -641,19 +641,25 @@
         <v>3769.9148500000001</v>
       </c>
       <c r="J4" s="4">
-        <v>10936.22</v>
+        <v>10936.2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+    <row r="5" spans="1:10">
+      <c r="A5" s="5">
+        <v>907675.67</v>
+      </c>
       <c r="B5" s="5">
         <v>2026</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3583.33</v>
+      </c>
       <c r="F5" s="5">
         <v>0</v>
       </c>
@@ -663,8 +669,18 @@
       <c r="H5" s="5">
         <v>0</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="I5" s="5">
+        <v>4538.38</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3583.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="J9" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manutencao\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA9231E-9E21-4CCE-BBCC-5FBAE5B8C672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -18,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -85,11 +75,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,14 +499,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="10" width="12.5" customWidth="1"/>
+    <col min="1" max="10" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42.75">
+    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,7 +538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>647585.69999999995</v>
       </c>
@@ -580,7 +570,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>844687.4</v>
       </c>
@@ -612,7 +602,7 @@
         <v>4845</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>753982.97</v>
       </c>
@@ -644,42 +634,42 @@
         <v>10936.2</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>907675.67</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2026</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
         <v>3583.33</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>4538.38</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>3583.33</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J9" s="7"/>
     </row>
   </sheetData>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA9231E-9E21-4CCE-BBCC-5FBAE5B8C672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C15789-78EE-41D4-815D-A28DF5C5492C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,7 +150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -165,6 +165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,25 +639,25 @@
       <c r="A5" s="4">
         <v>907675.67</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="8">
         <v>2026</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="6">
         <v>0</v>
       </c>
       <c r="E5" s="4">
         <v>3583.33</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
         <v>0</v>
       </c>
       <c r="I5" s="4">

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C15789-78EE-41D4-815D-A28DF5C5492C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0C88CA-B4C5-4A3A-A41F-99D2D88A2F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -501,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="12.44140625" customWidth="1"/>
@@ -667,11 +678,11 @@
         <v>3583.33</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J7" s="7"/>
+    </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J9" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Indicadores_manutencao/manutencao.xlsx
+++ b/data/Indicadores_manutencao/manutencao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\data\Indicadores_manutencao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0C88CA-B4C5-4A3A-A41F-99D2D88A2F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED981C7B-2D19-47A6-A744-FF864D4CEF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Faturamento Mensal</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Abril</t>
+  </si>
+  <si>
+    <t>Maio</t>
   </si>
 </sst>
 </file>
@@ -161,7 +164,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -177,6 +180,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -678,7 +683,42 @@
         <v>3583.33</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>884756.31</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4">
+        <v>7376</v>
+      </c>
+      <c r="E6" s="4">
+        <v>175</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>695.77</v>
+      </c>
+      <c r="I6" s="4">
+        <f>0.005*A6</f>
+        <v>4423.7815500000006</v>
+      </c>
+      <c r="J6" s="10">
+        <f>D6+E6+F6+G6+H6</f>
+        <v>8246.77</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I7" s="9"/>
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
